--- a/docs/par/specimen-hunter-par.xlsx
+++ b/docs/par/specimen-hunter-par.xlsx
@@ -13,10 +13,11 @@
     <sheet name="Line Wins Base" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Line Wins Free Spins" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Fish Values" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Baited Swims" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Free Spins Feature" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Win Distribution" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Strip Listing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Kingfisher" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Baited Swims" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Free Spins Feature" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Win Distribution" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Strip Listing" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,8 +140,9 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +160,7 @@
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -534,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -596,7 +599,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>'Line Wins Base'!E41+'Free Spins Feature'!B24</f>
+        <f>Kingfisher!$B$14+'Free Spins Feature'!B24</f>
         <v/>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.0008481649029764782</v>
+        <v>0.0008470766962981896</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -623,16 +626,16 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which base game line wins</t>
+          <t xml:space="preserve">  of which base game (line wins incl. kingfisher)</t>
         </is>
       </c>
       <c r="B8" s="7">
-        <f>'Line Wins Base'!E41</f>
+        <f>Kingfisher!$B$14</f>
         <v/>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Line Wins Base</t>
+          <t>Kingfisher</t>
         </is>
       </c>
     </row>
@@ -659,7 +662,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.9606714079772111</v>
+        <v>0.9630377100022699</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -674,7 +677,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.002457221232476998</v>
+        <v>0.00250048537228725</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -689,7 +692,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.2549386</v>
+        <v>0.25454346</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -716,43 +719,43 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Expected free spins per feature</t>
+          <t>Kingfisher: 1 in</t>
         </is>
       </c>
       <c r="B14" s="11">
-        <f>'Free Spins Feature'!B14</f>
+        <f>Kingfisher!B5</f>
         <v/>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>engine.js</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Expected feature win (x stake)</t>
+          <t>Kingfisher average line win (x stake)</t>
         </is>
       </c>
       <c r="B15" s="12">
-        <f>'Free Spins Feature'!B23</f>
+        <f>Kingfisher!D11</f>
         <v/>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Exact (uncapped)</t>
+          <t>Exact</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which baited swims (x stake)</t>
-        </is>
-      </c>
-      <c r="B16" s="12">
-        <f>'Free Spins Feature'!B22</f>
+          <t>Expected free spins per feature</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>'Free Spins Feature'!B14</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -764,57 +767,59 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Expected catches per swim per feature</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <f>'Baited Swims'!$B$34</f>
+          <t>Expected feature win (x stake)</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>'Free Spins Feature'!B23</f>
         <v/>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Exact (Baited Swims)</t>
+          <t>Exact (uncapped)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Volatility (standard deviation, x stake)</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>8.86488671612271</v>
+          <t xml:space="preserve">  of which baited swims (x stake)</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>'Free Spins Feature'!B22</f>
+        <v/>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Exact</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Returns below stake (0 &lt; win &lt; 1x)</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>0.11147428</v>
+          <t>Expected catches per swim per feature</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <f>'Baited Swims'!$B$34</f>
+        <v/>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Simulation; not celebrated (RTS 14F)</t>
+          <t>Exact (Baited Swims)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Highest win in simulation (x stake)</t>
+          <t>Volatility (standard deviation, x stake)</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>5000</v>
+        <v>9.020970219398382</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -825,26 +830,26 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Maximum win cap per round (x stake)</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>5000</v>
+          <t>Returns below stake (0 &lt; win &lt; 1x)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>0.10832966</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>engine.js MAX_WIN</t>
+          <t>Simulation; not celebrated (RTS 14F)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Rounds that hit the cap in simulation</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>12</v>
+          <t>Highest win in simulation (x stake)</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>5000</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -855,81 +860,111 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Features that reach the cap: 1 in</t>
+          <t>Maximum win cap per round (x stake)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>39840.64143426295</v>
+        <v>5000</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Cap simulation (features with no cap)</t>
+          <t>engine.js MAX_WIN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Rounds that reach the cap: 1 in</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>B23/'Free Spins Feature'!B8</f>
-        <v/>
+          <t>Rounds that hit the cap in simulation</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Features per cap hit / P(trigger)</t>
+          <t>Simulation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Features that reach the cap: 1 in</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>39920.16367265469</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Cap simulation (features with no cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Rounds that reach the cap: 1 in</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>B25/'Free Spins Feature'!B8</f>
+        <v/>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Features per cap hit / P(trigger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Stake range (GB)</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>£0.10 to £5.00 (£2.00 max for ages 18 to 24)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>GB online slots stake limits 2025; operator may set lower</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Colour key: blue = input from game files or simulation; black = formula; green = link to another sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Exact figures ignore the 5,000x cap. The simulation shows how rarely it is reached; its effect on RTP is a few thousandths of a percent.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Simulation uses the production engine (client/src/engine.js) with a seeded PRNG for repeatability.</t>
+          <t>Colour key: blue = input from game files or simulation; black = formula; green = link to another sheet.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Regenerate: node math/par_sheet.mjs 50000000 then python math/par_xlsx.py</t>
+          <t>Exact figures ignore the 5,000x cap. The simulation shows how rarely it is reached; its effect on RTP is a few thousandths of a percent.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Simulation uses the production engine (client/src/engine.js) with a seeded PRNG for repeatability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Regenerate: node math/par_sheet.mjs 50000000 then python math/par_xlsx.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>This is the developer's design PAR. Certification by a UKGC-approved test house is required before real-money use.</t>
         </is>
@@ -941,6 +976,377 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Win distribution (simulation of the production engine, 50,000,000 rounds, seed 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total win per game round (base spin + any free spins) as a multiple of stake. Rounds counted by math/par_sheet.mjs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rounds simulated</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Win band</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rounds</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1 in</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>RTP contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>No win</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>36970809</v>
+      </c>
+      <c r="C6" s="41">
+        <f>B6/$B$3</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>IF(B6=0,"-",$B$3/B6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Below stake (0 &lt; x &lt; 1)</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>5416483</v>
+      </c>
+      <c r="C7" s="41">
+        <f>B7/$B$3</f>
+        <v/>
+      </c>
+      <c r="D7" s="19">
+        <f>IF(B7=0,"-",$B$3/B7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.08024618400043074</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>1x to &lt;2x</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>3120748</v>
+      </c>
+      <c r="C8" s="41">
+        <f>B8/$B$3</f>
+        <v/>
+      </c>
+      <c r="D8" s="19">
+        <f>IF(B8=0,"-",$B$3/B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.09258057600030245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2x to &lt;5x</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>3230150</v>
+      </c>
+      <c r="C9" s="41">
+        <f>B9/$B$3</f>
+        <v/>
+      </c>
+      <c r="D9" s="19">
+        <f>IF(B9=0,"-",$B$3/B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.2020549300017867</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5x to &lt;10x</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>739947</v>
+      </c>
+      <c r="C10" s="41">
+        <f>B10/$B$3</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>IF(B10=0,"-",$B$3/B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.09965247400008118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10x to &lt;20x</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>157250</v>
+      </c>
+      <c r="C11" s="41">
+        <f>B11/$B$3</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>IF(B11=0,"-",$B$3/B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.0418080719999905</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>20x to &lt;50x</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>213927</v>
+      </c>
+      <c r="C12" s="41">
+        <f>B12/$B$3</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>IF(B12=0,"-",$B$3/B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.1423713780000114</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>50x to &lt;100x</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>110865</v>
+      </c>
+      <c r="C13" s="41">
+        <f>B13/$B$3</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>IF(B13=0,"-",$B$3/B13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.1519728159999991</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>100x to &lt;250x</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>33900</v>
+      </c>
+      <c r="C14" s="41">
+        <f>B14/$B$3</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>IF(B14=0,"-",$B$3/B14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.09524059200000132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>250x to &lt;500x</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>4592</v>
+      </c>
+      <c r="C15" s="41">
+        <f>B15/$B$3</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>IF(B15=0,"-",$B$3/B15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.02984283599999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>500x to &lt;1,000x</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>664</v>
+      </c>
+      <c r="C16" s="41">
+        <f>B16/$B$3</f>
+        <v/>
+      </c>
+      <c r="D16" s="19">
+        <f>IF(B16=0,"-",$B$3/B16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.008557239999999997</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>1,000x to &lt;5,000x</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>659</v>
+      </c>
+      <c r="C17" s="41">
+        <f>B17/$B$3</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>IF(B17=0,"-",$B$3/B17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.01811061200000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>5,000x (cap)</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="41">
+        <f>B18/$B$3</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>IF(B18=0,"-",$B$3/B18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B19" s="42">
+        <f>SUM(B6:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="26">
+        <f>SUM(C6:C18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>SUM(E6:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RTP contribution per band is the simulated sum of wins in that band divided by rounds (input from the simulation).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1029,1760 +1435,1760 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>BOILIE</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>BIVVY</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>CATAPULT</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>WILD</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>BOILIE</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="K4" s="19" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>ALARM</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>WILD</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>CORN</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>BIVVY</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>ROACH</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>CORN</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>BOILIE</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>ROACH</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>FLASK</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>ROACH</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>BREAM</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>FLASK</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>CORN</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>CATAPULT</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>CATAPULT</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>ROACH</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>BOILIE</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>BIVVY</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>CORN</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>WILD</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>CATAPULT</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>BOILIE</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>ALARM</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>MEAT</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>TENCH</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
         <is>
           <t>BOILIE</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="K9" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="L17" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="K25" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>BREAM</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="K29" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="L29" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="K30" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>MIRROR</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>ROACH</t>
-        </is>
-      </c>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>FLASK</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="H33" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>BIVVY</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>CORN</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>WILD</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>CATAPULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>PELLET</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>TENCH</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>ALARM</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>BOILIE</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
+      <c r="L35" s="20" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -2890,24 +3296,24 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <f>D5/10</f>
         <v/>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="21">
         <f>E5/10</f>
         <v/>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <f>F5/10</f>
         <v/>
       </c>
@@ -2928,24 +3334,24 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>D6/10</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>E6/10</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <f>F6/10</f>
         <v/>
       </c>
@@ -2966,24 +3372,24 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>D7/10</f>
         <v/>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="21">
         <f>E7/10</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <f>F7/10</f>
         <v/>
       </c>
@@ -2991,12 +3397,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
+          <t>Luncheon Meat</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>PELLET</t>
+          <t>MEAT</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3004,24 +3410,24 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <f>D8/10</f>
         <v/>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="21">
         <f>E8/10</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <f>F8/10</f>
         <v/>
       </c>
@@ -3042,24 +3448,24 @@
           <t>Mid</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>75</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>D9/10</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="21">
         <f>E9/10</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <f>F9/10</f>
         <v/>
       </c>
@@ -3080,24 +3486,24 @@
           <t>Mid</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>D10/10</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>E10/10</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="21">
         <f>F10/10</f>
         <v/>
       </c>
@@ -3118,24 +3524,24 @@
           <t>Mid</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>D11/10</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="21">
         <f>E11/10</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="21">
         <f>F11/10</f>
         <v/>
       </c>
@@ -3156,24 +3562,24 @@
           <t>Mid</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>D12/10</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>E12/10</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="21">
         <f>F12/10</f>
         <v/>
       </c>
@@ -3194,24 +3600,24 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="20" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>D13/10</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <f>E13/10</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <f>F13/10</f>
         <v/>
       </c>
@@ -3232,24 +3638,24 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>240</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>D14/10</f>
         <v/>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <f>E14/10</f>
         <v/>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="21">
         <f>F14/10</f>
         <v/>
       </c>
@@ -3270,24 +3676,24 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>360</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <f>D15/10</f>
         <v/>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <f>E15/10</f>
         <v/>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="21">
         <f>F15/10</f>
         <v/>
       </c>
@@ -3308,24 +3714,24 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>225</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <v>750</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>D16/10</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <f>E16/10</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <f>F16/10</f>
         <v/>
       </c>
@@ -3450,38 +3856,38 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="17" t="n">
+      <c r="B6" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="22">
         <f>B6/B$21</f>
         <v/>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="22">
         <f>C6/C$21</f>
         <v/>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="22">
         <f>D6/D$21</f>
         <v/>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="22">
         <f>E6/E$21</f>
         <v/>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="22">
         <f>F6/F$21</f>
         <v/>
       </c>
@@ -3492,38 +3898,38 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="17" t="n">
+      <c r="B7" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>B7/B$21</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>C7/C$21</f>
         <v/>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="22">
         <f>D7/D$21</f>
         <v/>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f>E7/E$21</f>
         <v/>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f>F7/F$21</f>
         <v/>
       </c>
@@ -3534,38 +3940,38 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <f>B8/B$21</f>
         <v/>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="22">
         <f>C8/C$21</f>
         <v/>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="22">
         <f>D8/D$21</f>
         <v/>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="22">
         <f>E8/E$21</f>
         <v/>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="22">
         <f>F8/F$21</f>
         <v/>
       </c>
@@ -3573,41 +3979,41 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="21">
+      <c r="H9" s="22">
         <f>B9/B$21</f>
         <v/>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="22">
         <f>C9/C$21</f>
         <v/>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="22">
         <f>D9/D$21</f>
         <v/>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="22">
         <f>E9/E$21</f>
         <v/>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="22">
         <f>F9/F$21</f>
         <v/>
       </c>
@@ -3618,38 +4024,38 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="22">
         <f>B10/B$21</f>
         <v/>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="22">
         <f>C10/C$21</f>
         <v/>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="22">
         <f>D10/D$21</f>
         <v/>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="22">
         <f>E10/E$21</f>
         <v/>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="22">
         <f>F10/F$21</f>
         <v/>
       </c>
@@ -3660,38 +4066,38 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <f>B11/B$21</f>
         <v/>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="22">
         <f>C11/C$21</f>
         <v/>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="22">
         <f>D11/D$21</f>
         <v/>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="22">
         <f>E11/E$21</f>
         <v/>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="22">
         <f>F11/F$21</f>
         <v/>
       </c>
@@ -3702,38 +4108,38 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="22">
         <f>B12/B$21</f>
         <v/>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <f>C12/C$21</f>
         <v/>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="22">
         <f>D12/D$21</f>
         <v/>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="22">
         <f>E12/E$21</f>
         <v/>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="22">
         <f>F12/F$21</f>
         <v/>
       </c>
@@ -3744,38 +4150,38 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="21">
+      <c r="H13" s="22">
         <f>B13/B$21</f>
         <v/>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="22">
         <f>C13/C$21</f>
         <v/>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="22">
         <f>D13/D$21</f>
         <v/>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="22">
         <f>E13/E$21</f>
         <v/>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="22">
         <f>F13/F$21</f>
         <v/>
       </c>
@@ -3786,38 +4192,38 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="22">
         <f>B14/B$21</f>
         <v/>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="22">
         <f>C14/C$21</f>
         <v/>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="22">
         <f>D14/D$21</f>
         <v/>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="22">
         <f>E14/E$21</f>
         <v/>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="22">
         <f>F14/F$21</f>
         <v/>
       </c>
@@ -3828,38 +4234,38 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="22">
         <f>B15/B$21</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="22">
         <f>C15/C$21</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="22">
         <f>D15/D$21</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="22">
         <f>E15/E$21</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="22">
         <f>F15/F$21</f>
         <v/>
       </c>
@@ -3870,38 +4276,38 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <f>B16/B$21</f>
         <v/>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="22">
         <f>C16/C$21</f>
         <v/>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="22">
         <f>D16/D$21</f>
         <v/>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="22">
         <f>E16/E$21</f>
         <v/>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="22">
         <f>F16/F$21</f>
         <v/>
       </c>
@@ -3912,38 +4318,38 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="22">
         <f>B17/B$21</f>
         <v/>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="22">
         <f>C17/C$21</f>
         <v/>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="22">
         <f>D17/D$21</f>
         <v/>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="22">
         <f>E17/E$21</f>
         <v/>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="22">
         <f>F17/F$21</f>
         <v/>
       </c>
@@ -3954,38 +4360,38 @@
           <t>Leather Carp (Wild)</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="22">
         <f>B18/B$21</f>
         <v/>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="22">
         <f>C18/C$21</f>
         <v/>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="22">
         <f>D18/D$21</f>
         <v/>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="22">
         <f>E18/E$21</f>
         <v/>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="22">
         <f>F18/F$21</f>
         <v/>
       </c>
@@ -3996,38 +4402,38 @@
           <t>Bite Alarm (Scatter)</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="22">
         <f>B19/B$21</f>
         <v/>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="22">
         <f>C19/C$21</f>
         <v/>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="22">
         <f>D19/D$21</f>
         <v/>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="22">
         <f>E19/E$21</f>
         <v/>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="22">
         <f>F19/F$21</f>
         <v/>
       </c>
@@ -4038,38 +4444,38 @@
           <t>Specimen Fish (Cash)</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="22">
         <f>B20/B$21</f>
         <v/>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="22">
         <f>C20/C$21</f>
         <v/>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="22">
         <f>D20/D$21</f>
         <v/>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="22">
         <f>E20/E$21</f>
         <v/>
       </c>
-      <c r="L20" s="21">
+      <c r="L20" s="22">
         <f>F20/F$21</f>
         <v/>
       </c>
@@ -4080,23 +4486,23 @@
           <t>Strip length</t>
         </is>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <f>SUM(B6:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>SUM(C6:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="19">
         <f>SUM(D6:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>SUM(E6:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>SUM(F6:F20)</f>
         <v/>
       </c>
@@ -4172,38 +4578,38 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="21">
+      <c r="H25" s="22">
         <f>B25/B$40</f>
         <v/>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="22">
         <f>C25/C$40</f>
         <v/>
       </c>
-      <c r="J25" s="21">
+      <c r="J25" s="22">
         <f>D25/D$40</f>
         <v/>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="22">
         <f>E25/E$40</f>
         <v/>
       </c>
-      <c r="L25" s="21">
+      <c r="L25" s="22">
         <f>F25/F$40</f>
         <v/>
       </c>
@@ -4214,38 +4620,38 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="17" t="n">
+      <c r="B26" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="22">
         <f>B26/B$40</f>
         <v/>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="22">
         <f>C26/C$40</f>
         <v/>
       </c>
-      <c r="J26" s="21">
+      <c r="J26" s="22">
         <f>D26/D$40</f>
         <v/>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="22">
         <f>E26/E$40</f>
         <v/>
       </c>
-      <c r="L26" s="21">
+      <c r="L26" s="22">
         <f>F26/F$40</f>
         <v/>
       </c>
@@ -4256,38 +4662,38 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="22">
         <f>B27/B$40</f>
         <v/>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="22">
         <f>C27/C$40</f>
         <v/>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="22">
         <f>D27/D$40</f>
         <v/>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="22">
         <f>E27/E$40</f>
         <v/>
       </c>
-      <c r="L27" s="21">
+      <c r="L27" s="22">
         <f>F27/F$40</f>
         <v/>
       </c>
@@ -4295,41 +4701,41 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="21">
+      <c r="H28" s="22">
         <f>B28/B$40</f>
         <v/>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="22">
         <f>C28/C$40</f>
         <v/>
       </c>
-      <c r="J28" s="21">
+      <c r="J28" s="22">
         <f>D28/D$40</f>
         <v/>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="22">
         <f>E28/E$40</f>
         <v/>
       </c>
-      <c r="L28" s="21">
+      <c r="L28" s="22">
         <f>F28/F$40</f>
         <v/>
       </c>
@@ -4340,38 +4746,38 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="22">
         <f>B29/B$40</f>
         <v/>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="22">
         <f>C29/C$40</f>
         <v/>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="22">
         <f>D29/D$40</f>
         <v/>
       </c>
-      <c r="K29" s="21">
+      <c r="K29" s="22">
         <f>E29/E$40</f>
         <v/>
       </c>
-      <c r="L29" s="21">
+      <c r="L29" s="22">
         <f>F29/F$40</f>
         <v/>
       </c>
@@ -4382,38 +4788,38 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="22">
         <f>B30/B$40</f>
         <v/>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="22">
         <f>C30/C$40</f>
         <v/>
       </c>
-      <c r="J30" s="21">
+      <c r="J30" s="22">
         <f>D30/D$40</f>
         <v/>
       </c>
-      <c r="K30" s="21">
+      <c r="K30" s="22">
         <f>E30/E$40</f>
         <v/>
       </c>
-      <c r="L30" s="21">
+      <c r="L30" s="22">
         <f>F30/F$40</f>
         <v/>
       </c>
@@ -4424,38 +4830,38 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="22">
         <f>B31/B$40</f>
         <v/>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="22">
         <f>C31/C$40</f>
         <v/>
       </c>
-      <c r="J31" s="21">
+      <c r="J31" s="22">
         <f>D31/D$40</f>
         <v/>
       </c>
-      <c r="K31" s="21">
+      <c r="K31" s="22">
         <f>E31/E$40</f>
         <v/>
       </c>
-      <c r="L31" s="21">
+      <c r="L31" s="22">
         <f>F31/F$40</f>
         <v/>
       </c>
@@ -4466,38 +4872,38 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="D32" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="E32" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="F32" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="21">
+      <c r="H32" s="22">
         <f>B32/B$40</f>
         <v/>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="22">
         <f>C32/C$40</f>
         <v/>
       </c>
-      <c r="J32" s="21">
+      <c r="J32" s="22">
         <f>D32/D$40</f>
         <v/>
       </c>
-      <c r="K32" s="21">
+      <c r="K32" s="22">
         <f>E32/E$40</f>
         <v/>
       </c>
-      <c r="L32" s="21">
+      <c r="L32" s="22">
         <f>F32/F$40</f>
         <v/>
       </c>
@@ -4508,38 +4914,38 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B33" s="17" t="n">
+      <c r="B33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="17" t="n">
+      <c r="E33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="22">
         <f>B33/B$40</f>
         <v/>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="22">
         <f>C33/C$40</f>
         <v/>
       </c>
-      <c r="J33" s="21">
+      <c r="J33" s="22">
         <f>D33/D$40</f>
         <v/>
       </c>
-      <c r="K33" s="21">
+      <c r="K33" s="22">
         <f>E33/E$40</f>
         <v/>
       </c>
-      <c r="L33" s="21">
+      <c r="L33" s="22">
         <f>F33/F$40</f>
         <v/>
       </c>
@@ -4550,38 +4956,38 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="22">
         <f>B34/B$40</f>
         <v/>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="22">
         <f>C34/C$40</f>
         <v/>
       </c>
-      <c r="J34" s="21">
+      <c r="J34" s="22">
         <f>D34/D$40</f>
         <v/>
       </c>
-      <c r="K34" s="21">
+      <c r="K34" s="22">
         <f>E34/E$40</f>
         <v/>
       </c>
-      <c r="L34" s="21">
+      <c r="L34" s="22">
         <f>F34/F$40</f>
         <v/>
       </c>
@@ -4592,38 +4998,38 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="22">
         <f>B35/B$40</f>
         <v/>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="22">
         <f>C35/C$40</f>
         <v/>
       </c>
-      <c r="J35" s="21">
+      <c r="J35" s="22">
         <f>D35/D$40</f>
         <v/>
       </c>
-      <c r="K35" s="21">
+      <c r="K35" s="22">
         <f>E35/E$40</f>
         <v/>
       </c>
-      <c r="L35" s="21">
+      <c r="L35" s="22">
         <f>F35/F$40</f>
         <v/>
       </c>
@@ -4634,38 +5040,38 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="22">
         <f>B36/B$40</f>
         <v/>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="22">
         <f>C36/C$40</f>
         <v/>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="22">
         <f>D36/D$40</f>
         <v/>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="22">
         <f>E36/E$40</f>
         <v/>
       </c>
-      <c r="L36" s="21">
+      <c r="L36" s="22">
         <f>F36/F$40</f>
         <v/>
       </c>
@@ -4676,38 +5082,38 @@
           <t>Leather Carp (Wild)</t>
         </is>
       </c>
-      <c r="B37" s="17" t="n">
+      <c r="B37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="17" t="n">
+      <c r="C37" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E37" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="22">
         <f>B37/B$40</f>
         <v/>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="22">
         <f>C37/C$40</f>
         <v/>
       </c>
-      <c r="J37" s="21">
+      <c r="J37" s="22">
         <f>D37/D$40</f>
         <v/>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="22">
         <f>E37/E$40</f>
         <v/>
       </c>
-      <c r="L37" s="21">
+      <c r="L37" s="22">
         <f>F37/F$40</f>
         <v/>
       </c>
@@ -4718,38 +5124,38 @@
           <t>Bite Alarm (Scatter)</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="17" t="n">
+      <c r="C38" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="22">
         <f>B38/B$40</f>
         <v/>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="22">
         <f>C38/C$40</f>
         <v/>
       </c>
-      <c r="J38" s="21">
+      <c r="J38" s="22">
         <f>D38/D$40</f>
         <v/>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="22">
         <f>E38/E$40</f>
         <v/>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="22">
         <f>F38/F$40</f>
         <v/>
       </c>
@@ -4760,38 +5166,38 @@
           <t>Specimen Fish (Cash)</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="17" t="n">
+      <c r="E39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="17" t="n">
+      <c r="F39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="22">
         <f>B39/B$40</f>
         <v/>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="22">
         <f>C39/C$40</f>
         <v/>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="22">
         <f>D39/D$40</f>
         <v/>
       </c>
-      <c r="K39" s="21">
+      <c r="K39" s="22">
         <f>E39/E$40</f>
         <v/>
       </c>
-      <c r="L39" s="21">
+      <c r="L39" s="22">
         <f>F39/F$40</f>
         <v/>
       </c>
@@ -4802,23 +5208,23 @@
           <t>Strip length</t>
         </is>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="19">
         <f>SUM(B25:B39)</f>
         <v/>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="19">
         <f>SUM(C25:C39)</f>
         <v/>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="19">
         <f>SUM(D25:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="19">
         <f>SUM(E25:E39)</f>
         <v/>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="19">
         <f>SUM(F25:F39)</f>
         <v/>
       </c>
@@ -4859,6 +5265,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ordinary base spins, before the kingfisher (see the Kingfisher sheet for how it changes the base game).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4897,10 +5310,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="23">
         <f>'Reel Strips'!$H$6*('Reel Strips'!$I$6+'Reel Strips'!$I$18)*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$6-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$6*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$6-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$6*(1-'Reel Strips'!$K$6-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -4908,12 +5321,12 @@
         <f>Paytable!G5</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <f>C5*D5*10</f>
         <v/>
       </c>
-      <c r="F5" s="24" t="n">
-        <v>0.00446319580078125</v>
+      <c r="F5" s="25" t="n">
+        <v>0.0053558349609375</v>
       </c>
     </row>
     <row r="6">
@@ -4922,10 +5335,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>'Reel Strips'!$H$6*('Reel Strips'!$I$6+'Reel Strips'!$I$18)*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$6-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$6*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$6-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$6*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$6-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$6*(1-'Reel Strips'!$L$6-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -4933,12 +5346,12 @@
         <f>Paytable!H5</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="24">
         <f>C6*D6*10</f>
         <v/>
       </c>
-      <c r="F6" s="24" t="n">
-        <v>0.0008368492126464844</v>
+      <c r="F6" s="25" t="n">
+        <v>0.001004219055175781</v>
       </c>
     </row>
     <row r="7">
@@ -4947,10 +5360,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <f>'Reel Strips'!$H$6*('Reel Strips'!$I$6+'Reel Strips'!$I$18)*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*('Reel Strips'!$L$6+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$6*('Reel Strips'!$J$6+'Reel Strips'!$J$18)*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*('Reel Strips'!$L$6+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$6*('Reel Strips'!$K$6+'Reel Strips'!$K$18)*('Reel Strips'!$L$6+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$6*('Reel Strips'!$L$6+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$6</f>
         <v/>
       </c>
@@ -4958,12 +5371,12 @@
         <f>Paytable!I5</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <f>C7*D7*10</f>
         <v/>
       </c>
-      <c r="F7" s="24" t="n">
-        <v>0.0001931190490722656</v>
+      <c r="F7" s="25" t="n">
+        <v>0.0002317428588867188</v>
       </c>
     </row>
     <row r="8">
@@ -4972,10 +5385,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <f>'Reel Strips'!$H$7*('Reel Strips'!$I$7+'Reel Strips'!$I$18)*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$7-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$7*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$7-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$7*(1-'Reel Strips'!$K$7-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -4983,12 +5396,12 @@
         <f>Paytable!G6</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <f>C8*D8*10</f>
         <v/>
       </c>
-      <c r="F8" s="24" t="n">
-        <v>0.00446319580078125</v>
+      <c r="F8" s="25" t="n">
+        <v>0.0053558349609375</v>
       </c>
     </row>
     <row r="9">
@@ -4997,10 +5410,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>'Reel Strips'!$H$7*('Reel Strips'!$I$7+'Reel Strips'!$I$18)*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$7-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$7*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$7-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$7*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$7-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$7*(1-'Reel Strips'!$L$7-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5008,12 +5421,12 @@
         <f>Paytable!H6</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <f>C9*D9*10</f>
         <v/>
       </c>
-      <c r="F9" s="24" t="n">
-        <v>0.0008368492126464844</v>
+      <c r="F9" s="25" t="n">
+        <v>0.001004219055175781</v>
       </c>
     </row>
     <row r="10">
@@ -5022,10 +5435,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'Reel Strips'!$H$7*('Reel Strips'!$I$7+'Reel Strips'!$I$18)*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*('Reel Strips'!$L$7+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$7*('Reel Strips'!$J$7+'Reel Strips'!$J$18)*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*('Reel Strips'!$L$7+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$7*('Reel Strips'!$K$7+'Reel Strips'!$K$18)*('Reel Strips'!$L$7+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$7*('Reel Strips'!$L$7+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$7</f>
         <v/>
       </c>
@@ -5033,12 +5446,12 @@
         <f>Paytable!I6</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <f>C10*D10*10</f>
         <v/>
       </c>
-      <c r="F10" s="24" t="n">
-        <v>0.0001931190490722656</v>
+      <c r="F10" s="25" t="n">
+        <v>0.0002317428588867188</v>
       </c>
     </row>
     <row r="11">
@@ -5047,10 +5460,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>'Reel Strips'!$H$8*('Reel Strips'!$I$8+'Reel Strips'!$I$18)*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$8-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$8*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$8-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$8*(1-'Reel Strips'!$K$8-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5058,11 +5471,11 @@
         <f>Paytable!G7</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <f>C11*D11*10</f>
         <v/>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="25" t="n">
         <v>0.004673004150390625</v>
       </c>
     </row>
@@ -5072,10 +5485,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>'Reel Strips'!$H$8*('Reel Strips'!$I$8+'Reel Strips'!$I$18)*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$8-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$8*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$8-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$8*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$8-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$8*(1-'Reel Strips'!$L$8-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5083,11 +5496,11 @@
         <f>Paytable!H7</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>C12*D12*10</f>
         <v/>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>0.001063108444213867</v>
       </c>
     </row>
@@ -5097,10 +5510,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>'Reel Strips'!$H$8*('Reel Strips'!$I$8+'Reel Strips'!$I$18)*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*('Reel Strips'!$L$8+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$8*('Reel Strips'!$J$8+'Reel Strips'!$J$18)*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*('Reel Strips'!$L$8+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$8*('Reel Strips'!$K$8+'Reel Strips'!$K$18)*('Reel Strips'!$L$8+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$8*('Reel Strips'!$L$8+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$8</f>
         <v/>
       </c>
@@ -5108,24 +5521,24 @@
         <f>Paytable!I7</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <f>C13*D13*10</f>
         <v/>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>0.0002453327178955078</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>'Reel Strips'!$H$9*('Reel Strips'!$I$9+'Reel Strips'!$I$18)*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$9-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$9*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$9-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$9*(1-'Reel Strips'!$K$9-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5133,24 +5546,24 @@
         <f>Paytable!G8</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>C14*D14*10</f>
         <v/>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.004673004150390625</v>
+      <c r="F14" s="25" t="n">
+        <v>0.003504753112792969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>'Reel Strips'!$H$9*('Reel Strips'!$I$9+'Reel Strips'!$I$18)*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$9-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$9*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$9-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$9*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$9-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$9*(1-'Reel Strips'!$L$9-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5158,24 +5571,24 @@
         <f>Paytable!H8</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>C15*D15*10</f>
         <v/>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>0.001063108444213867</v>
+      <c r="F15" s="25" t="n">
+        <v>0.0007973313331604004</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <f>'Reel Strips'!$H$9*('Reel Strips'!$I$9+'Reel Strips'!$I$18)*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*('Reel Strips'!$L$9+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$9*('Reel Strips'!$J$9+'Reel Strips'!$J$18)*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*('Reel Strips'!$L$9+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$9*('Reel Strips'!$K$9+'Reel Strips'!$K$18)*('Reel Strips'!$L$9+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$9*('Reel Strips'!$L$9+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$9</f>
         <v/>
       </c>
@@ -5183,12 +5596,12 @@
         <f>Paytable!I8</f>
         <v/>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <f>C16*D16*10</f>
         <v/>
       </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0002453327178955078</v>
+      <c r="F16" s="25" t="n">
+        <v>0.0001839995384216309</v>
       </c>
     </row>
     <row r="17">
@@ -5197,10 +5610,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>'Reel Strips'!$H$10*('Reel Strips'!$I$10+'Reel Strips'!$I$18)*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$10-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$10*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$10-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$10*(1-'Reel Strips'!$K$10-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5208,11 +5621,11 @@
         <f>Paytable!G9</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>C17*D17*10</f>
         <v/>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="25" t="n">
         <v>0.00267791748046875</v>
       </c>
     </row>
@@ -5222,10 +5635,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="23">
         <f>'Reel Strips'!$H$10*('Reel Strips'!$I$10+'Reel Strips'!$I$18)*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$10-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$10*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$10-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$10*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$10-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$10*(1-'Reel Strips'!$L$10-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5233,11 +5646,11 @@
         <f>Paytable!H9</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>C18*D18*10</f>
         <v/>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="25" t="n">
         <v>0.0005214214324951172</v>
       </c>
     </row>
@@ -5247,10 +5660,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <f>'Reel Strips'!$H$10*('Reel Strips'!$I$10+'Reel Strips'!$I$18)*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*('Reel Strips'!$L$10+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$10*('Reel Strips'!$J$10+'Reel Strips'!$J$18)*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*('Reel Strips'!$L$10+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$10*('Reel Strips'!$K$10+'Reel Strips'!$K$18)*('Reel Strips'!$L$10+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$10*('Reel Strips'!$L$10+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$10</f>
         <v/>
       </c>
@@ -5258,11 +5671,11 @@
         <f>Paytable!I9</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>C19*D19*10</f>
         <v/>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="25" t="n">
         <v>9.655952453613281e-05</v>
       </c>
     </row>
@@ -5272,10 +5685,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>'Reel Strips'!$H$11*('Reel Strips'!$I$11+'Reel Strips'!$I$18)*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$11-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$11*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$11-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$11*(1-'Reel Strips'!$K$11-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5283,11 +5696,11 @@
         <f>Paytable!G10</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>C20*D20*10</f>
         <v/>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="25" t="n">
         <v>0.001931190490722656</v>
       </c>
     </row>
@@ -5297,10 +5710,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <f>'Reel Strips'!$H$11*('Reel Strips'!$I$11+'Reel Strips'!$I$18)*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$11-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$11*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$11-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$11*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$11-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$11*(1-'Reel Strips'!$L$11-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5308,11 +5721,11 @@
         <f>Paytable!H10</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <f>C21*D21*10</f>
         <v/>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="25" t="n">
         <v>0.000301748514175415</v>
       </c>
     </row>
@@ -5322,10 +5735,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>'Reel Strips'!$H$11*('Reel Strips'!$I$11+'Reel Strips'!$I$18)*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*('Reel Strips'!$L$11+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$11*('Reel Strips'!$J$11+'Reel Strips'!$J$18)*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*('Reel Strips'!$L$11+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$11*('Reel Strips'!$K$11+'Reel Strips'!$K$18)*('Reel Strips'!$L$11+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$11*('Reel Strips'!$L$11+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$11</f>
         <v/>
       </c>
@@ -5333,11 +5746,11 @@
         <f>Paytable!I10</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <f>C22*D22*10</f>
         <v/>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="25" t="n">
         <v>5.587935447692871e-05</v>
       </c>
     </row>
@@ -5347,10 +5760,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>'Reel Strips'!$H$12*('Reel Strips'!$I$12+'Reel Strips'!$I$18)*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$12-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$12*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$12-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$12*(1-'Reel Strips'!$K$12-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5358,11 +5771,11 @@
         <f>Paytable!G11</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <f>C23*D23*10</f>
         <v/>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="25" t="n">
         <v>0.001287460327148438</v>
       </c>
     </row>
@@ -5372,10 +5785,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>'Reel Strips'!$H$12*('Reel Strips'!$I$12+'Reel Strips'!$I$18)*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$12-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$12*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$12-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$12*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$12-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$12*(1-'Reel Strips'!$L$12-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5383,11 +5796,11 @@
         <f>Paytable!H11</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <f>C24*D24*10</f>
         <v/>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="25" t="n">
         <v>0.0002086162567138672</v>
       </c>
     </row>
@@ -5397,10 +5810,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>'Reel Strips'!$H$12*('Reel Strips'!$I$12+'Reel Strips'!$I$18)*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*('Reel Strips'!$L$12+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$12*('Reel Strips'!$J$12+'Reel Strips'!$J$18)*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*('Reel Strips'!$L$12+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$12*('Reel Strips'!$K$12+'Reel Strips'!$K$18)*('Reel Strips'!$L$12+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$12*('Reel Strips'!$L$12+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$12</f>
         <v/>
       </c>
@@ -5408,11 +5821,11 @@
         <f>Paytable!I11</f>
         <v/>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <f>C25*D25*10</f>
         <v/>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>2.980232238769531e-05</v>
       </c>
     </row>
@@ -5422,10 +5835,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>'Reel Strips'!$H$13*('Reel Strips'!$I$13+'Reel Strips'!$I$18)*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$13-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$13*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$13-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$13*(1-'Reel Strips'!$K$13-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5433,12 +5846,12 @@
         <f>Paytable!G12</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <f>C26*D26*10</f>
         <v/>
       </c>
-      <c r="F26" s="24" t="n">
-        <v>0.001287460327148438</v>
+      <c r="F26" s="25" t="n">
+        <v>0.0006437301635742188</v>
       </c>
     </row>
     <row r="27">
@@ -5447,10 +5860,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>'Reel Strips'!$H$13*('Reel Strips'!$I$13+'Reel Strips'!$I$18)*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$13-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$13*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$13-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$13*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$13-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$13*(1-'Reel Strips'!$L$13-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5458,12 +5871,12 @@
         <f>Paytable!H12</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>C27*D27*10</f>
         <v/>
       </c>
-      <c r="F27" s="24" t="n">
-        <v>0.0002086162567138672</v>
+      <c r="F27" s="25" t="n">
+        <v>0.0001043081283569336</v>
       </c>
     </row>
     <row r="28">
@@ -5472,10 +5885,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>'Reel Strips'!$H$13*('Reel Strips'!$I$13+'Reel Strips'!$I$18)*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*('Reel Strips'!$L$13+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$13*('Reel Strips'!$J$13+'Reel Strips'!$J$18)*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*('Reel Strips'!$L$13+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$13*('Reel Strips'!$K$13+'Reel Strips'!$K$18)*('Reel Strips'!$L$13+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$13*('Reel Strips'!$L$13+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$13</f>
         <v/>
       </c>
@@ -5483,12 +5896,12 @@
         <f>Paytable!I12</f>
         <v/>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="24">
         <f>C28*D28*10</f>
         <v/>
       </c>
-      <c r="F28" s="24" t="n">
-        <v>2.980232238769531e-05</v>
+      <c r="F28" s="25" t="n">
+        <v>1.490116119384766e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5497,10 +5910,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="23">
         <f>'Reel Strips'!$H$14*('Reel Strips'!$I$14+'Reel Strips'!$I$18)*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$14-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$14*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$14-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$14*(1-'Reel Strips'!$K$14-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5508,11 +5921,11 @@
         <f>Paytable!G13</f>
         <v/>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <f>C29*D29*10</f>
         <v/>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -5522,10 +5935,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="23">
         <f>'Reel Strips'!$H$14*('Reel Strips'!$I$14+'Reel Strips'!$I$18)*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$14-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$14*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$14-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$14*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$14-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$14*(1-'Reel Strips'!$L$14-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5533,11 +5946,11 @@
         <f>Paytable!H13</f>
         <v/>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="24">
         <f>C30*D30*10</f>
         <v/>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -5547,10 +5960,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>'Reel Strips'!$H$14*('Reel Strips'!$I$14+'Reel Strips'!$I$18)*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*('Reel Strips'!$L$14+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$14*('Reel Strips'!$J$14+'Reel Strips'!$J$18)*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*('Reel Strips'!$L$14+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$14*('Reel Strips'!$K$14+'Reel Strips'!$K$18)*('Reel Strips'!$L$14+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$14*('Reel Strips'!$L$14+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$14</f>
         <v/>
       </c>
@@ -5558,11 +5971,11 @@
         <f>Paytable!I13</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="24">
         <f>C31*D31*10</f>
         <v/>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -5572,10 +5985,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <f>'Reel Strips'!$H$15*('Reel Strips'!$I$15+'Reel Strips'!$I$18)*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$15-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$15*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$15-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$15*(1-'Reel Strips'!$K$15-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5583,11 +5996,11 @@
         <f>Paytable!G14</f>
         <v/>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="24">
         <f>C32*D32*10</f>
         <v/>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -5597,10 +6010,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="23">
         <f>'Reel Strips'!$H$15*('Reel Strips'!$I$15+'Reel Strips'!$I$18)*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$15-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$15*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$15-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$15*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$15-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$15*(1-'Reel Strips'!$L$15-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5608,11 +6021,11 @@
         <f>Paytable!H14</f>
         <v/>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="24">
         <f>C33*D33*10</f>
         <v/>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -5622,10 +6035,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="23">
         <f>'Reel Strips'!$H$15*('Reel Strips'!$I$15+'Reel Strips'!$I$18)*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*('Reel Strips'!$L$15+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$15*('Reel Strips'!$J$15+'Reel Strips'!$J$18)*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*('Reel Strips'!$L$15+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$15*('Reel Strips'!$K$15+'Reel Strips'!$K$18)*('Reel Strips'!$L$15+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$15*('Reel Strips'!$L$15+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$15</f>
         <v/>
       </c>
@@ -5633,11 +6046,11 @@
         <f>Paytable!I14</f>
         <v/>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="24">
         <f>C34*D34*10</f>
         <v/>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -5647,10 +6060,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <f>'Reel Strips'!$H$16*('Reel Strips'!$I$16+'Reel Strips'!$I$18)*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$16-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$16*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$16-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$16*(1-'Reel Strips'!$K$16-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5658,11 +6071,11 @@
         <f>Paytable!G15</f>
         <v/>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="24">
         <f>C35*D35*10</f>
         <v/>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -5672,10 +6085,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>'Reel Strips'!$H$16*('Reel Strips'!$I$16+'Reel Strips'!$I$18)*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$16-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$16*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$16-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$16*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$16-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$16*(1-'Reel Strips'!$L$16-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5683,11 +6096,11 @@
         <f>Paytable!H15</f>
         <v/>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="24">
         <f>C36*D36*10</f>
         <v/>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -5697,10 +6110,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="23">
         <f>'Reel Strips'!$H$16*('Reel Strips'!$I$16+'Reel Strips'!$I$18)*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*('Reel Strips'!$L$16+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$16*('Reel Strips'!$J$16+'Reel Strips'!$J$18)*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*('Reel Strips'!$L$16+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$16*('Reel Strips'!$K$16+'Reel Strips'!$K$18)*('Reel Strips'!$L$16+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$16*('Reel Strips'!$L$16+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$16</f>
         <v/>
       </c>
@@ -5708,11 +6121,11 @@
         <f>Paytable!I15</f>
         <v/>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="24">
         <f>C37*D37*10</f>
         <v/>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -5722,10 +6135,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>'Reel Strips'!$H$17*('Reel Strips'!$I$17+'Reel Strips'!$I$18)*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$17-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$17*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*(1-'Reel Strips'!$K$17-'Reel Strips'!$K$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$17*(1-'Reel Strips'!$K$17-'Reel Strips'!$K$18)</f>
         <v/>
       </c>
@@ -5733,11 +6146,11 @@
         <f>Paytable!G16</f>
         <v/>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="24">
         <f>C38*D38*10</f>
         <v/>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -5747,10 +6160,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>'Reel Strips'!$H$17*('Reel Strips'!$I$17+'Reel Strips'!$I$18)*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$17-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$17*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$17-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$17*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*(1-'Reel Strips'!$L$17-'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$17*(1-'Reel Strips'!$L$17-'Reel Strips'!$L$18)</f>
         <v/>
       </c>
@@ -5758,11 +6171,11 @@
         <f>Paytable!H16</f>
         <v/>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="24">
         <f>C39*D39*10</f>
         <v/>
       </c>
-      <c r="F39" s="24" t="n">
+      <c r="F39" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -5772,10 +6185,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B40" s="18" t="n">
+      <c r="B40" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>'Reel Strips'!$H$17*('Reel Strips'!$I$17+'Reel Strips'!$I$18)*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*('Reel Strips'!$L$17+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$17*('Reel Strips'!$J$17+'Reel Strips'!$J$18)*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*('Reel Strips'!$L$17+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$17*('Reel Strips'!$K$17+'Reel Strips'!$K$18)*('Reel Strips'!$L$17+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$17*('Reel Strips'!$L$17+'Reel Strips'!$L$18)+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$17+'Reel Strips'!$H$18*'Reel Strips'!$I$18*'Reel Strips'!$J$18*'Reel Strips'!$K$18*'Reel Strips'!$L$18</f>
         <v/>
       </c>
@@ -5783,11 +6196,11 @@
         <f>Paytable!I16</f>
         <v/>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="24">
         <f>C40*D40*10</f>
         <v/>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -5797,7 +6210,7 @@
           <t>Total line RTP</t>
         </is>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="26">
         <f>SUM(E5:E40)</f>
         <v/>
       </c>
@@ -5808,7 +6221,7 @@
           <t>Max difference vs engine exact (should be ~0)</t>
         </is>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <f>SUMPRODUCT(ABS(C5:C40-F5:F40))</f>
         <v/>
       </c>
@@ -5894,10 +6307,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="23">
         <f>'Reel Strips'!$H$25*('Reel Strips'!$I$25+'Reel Strips'!$I$37)*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$25-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$25*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$25-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$25*(1-'Reel Strips'!$K$25-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -5905,12 +6318,12 @@
         <f>Paytable!G5</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <f>C5*D5*10</f>
         <v/>
       </c>
-      <c r="F5" s="24" t="n">
-        <v>0.001931190490722656</v>
+      <c r="F5" s="25" t="n">
+        <v>0.002574920654296875</v>
       </c>
     </row>
     <row r="6">
@@ -5919,10 +6332,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>'Reel Strips'!$H$25*('Reel Strips'!$I$25+'Reel Strips'!$I$37)*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$25-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$25*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$25-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$25*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$25-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$25*(1-'Reel Strips'!$L$25-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -5930,12 +6343,12 @@
         <f>Paytable!H5</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="24">
         <f>C6*D6*10</f>
         <v/>
       </c>
-      <c r="F6" s="24" t="n">
-        <v>0.000301748514175415</v>
+      <c r="F6" s="25" t="n">
+        <v>0.0004023313522338867</v>
       </c>
     </row>
     <row r="7">
@@ -5944,10 +6357,10 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <f>'Reel Strips'!$H$25*('Reel Strips'!$I$25+'Reel Strips'!$I$37)*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*('Reel Strips'!$L$25+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$25*('Reel Strips'!$J$25+'Reel Strips'!$J$37)*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*('Reel Strips'!$L$25+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$25*('Reel Strips'!$K$25+'Reel Strips'!$K$37)*('Reel Strips'!$L$25+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$25*('Reel Strips'!$L$25+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$25</f>
         <v/>
       </c>
@@ -5955,12 +6368,12 @@
         <f>Paytable!I5</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <f>C7*D7*10</f>
         <v/>
       </c>
-      <c r="F7" s="24" t="n">
-        <v>5.587935447692871e-05</v>
+      <c r="F7" s="25" t="n">
+        <v>7.450580596923828e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5969,10 +6382,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <f>'Reel Strips'!$H$26*('Reel Strips'!$I$26+'Reel Strips'!$I$37)*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$26-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$26*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$26-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$26*(1-'Reel Strips'!$K$26-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -5980,12 +6393,12 @@
         <f>Paytable!G6</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <f>C8*D8*10</f>
         <v/>
       </c>
-      <c r="F8" s="24" t="n">
-        <v>0.003570556640625</v>
+      <c r="F8" s="25" t="n">
+        <v>0.00446319580078125</v>
       </c>
     </row>
     <row r="9">
@@ -5994,10 +6407,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>'Reel Strips'!$H$26*('Reel Strips'!$I$26+'Reel Strips'!$I$37)*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$26-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$26*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$26-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$26*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$26-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$26*(1-'Reel Strips'!$L$26-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6005,12 +6418,12 @@
         <f>Paytable!H6</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <f>C9*D9*10</f>
         <v/>
       </c>
-      <c r="F9" s="24" t="n">
-        <v>0.0006952285766601562</v>
+      <c r="F9" s="25" t="n">
+        <v>0.0008690357208251953</v>
       </c>
     </row>
     <row r="10">
@@ -6019,10 +6432,10 @@
           <t>Boilies</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'Reel Strips'!$H$26*('Reel Strips'!$I$26+'Reel Strips'!$I$37)*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*('Reel Strips'!$L$26+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$26*('Reel Strips'!$J$26+'Reel Strips'!$J$37)*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*('Reel Strips'!$L$26+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$26*('Reel Strips'!$K$26+'Reel Strips'!$K$37)*('Reel Strips'!$L$26+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$26*('Reel Strips'!$L$26+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$26</f>
         <v/>
       </c>
@@ -6030,12 +6443,12 @@
         <f>Paytable!I6</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <f>C10*D10*10</f>
         <v/>
       </c>
-      <c r="F10" s="24" t="n">
-        <v>0.0001287460327148438</v>
+      <c r="F10" s="25" t="n">
+        <v>0.0001609325408935547</v>
       </c>
     </row>
     <row r="11">
@@ -6044,10 +6457,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>'Reel Strips'!$H$27*('Reel Strips'!$I$27+'Reel Strips'!$I$37)*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$27-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$27*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$27-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$27*(1-'Reel Strips'!$K$27-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6055,11 +6468,11 @@
         <f>Paytable!G7</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <f>C11*D11*10</f>
         <v/>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="25" t="n">
         <v>0.003570556640625</v>
       </c>
     </row>
@@ -6069,10 +6482,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>'Reel Strips'!$H$27*('Reel Strips'!$I$27+'Reel Strips'!$I$37)*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$27-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$27*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$27-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$27*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$27-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$27*(1-'Reel Strips'!$L$27-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6080,11 +6493,11 @@
         <f>Paytable!H7</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>C12*D12*10</f>
         <v/>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>0.0006952285766601562</v>
       </c>
     </row>
@@ -6094,10 +6507,10 @@
           <t>Sweetcorn</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>'Reel Strips'!$H$27*('Reel Strips'!$I$27+'Reel Strips'!$I$37)*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*('Reel Strips'!$L$27+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$27*('Reel Strips'!$J$27+'Reel Strips'!$J$37)*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*('Reel Strips'!$L$27+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$27*('Reel Strips'!$K$27+'Reel Strips'!$K$37)*('Reel Strips'!$L$27+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$27*('Reel Strips'!$L$27+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$27</f>
         <v/>
       </c>
@@ -6105,24 +6518,24 @@
         <f>Paytable!I7</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <f>C13*D13*10</f>
         <v/>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>0.0001287460327148438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>'Reel Strips'!$H$28*('Reel Strips'!$I$28+'Reel Strips'!$I$37)*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$28-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$28*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$28-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$28*(1-'Reel Strips'!$K$28-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6130,24 +6543,24 @@
         <f>Paytable!G8</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>C14*D14*10</f>
         <v/>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.003570556640625</v>
+      <c r="F14" s="25" t="n">
+        <v>0.00267791748046875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>'Reel Strips'!$H$28*('Reel Strips'!$I$28+'Reel Strips'!$I$37)*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$28-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$28*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$28-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$28*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$28-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$28*(1-'Reel Strips'!$L$28-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6155,24 +6568,24 @@
         <f>Paytable!H8</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>C15*D15*10</f>
         <v/>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>0.0006694793701171875</v>
+      <c r="F15" s="25" t="n">
+        <v>0.0005021095275878906</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Pellets</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
+          <t>Luncheon Meat</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <f>'Reel Strips'!$H$28*('Reel Strips'!$I$28+'Reel Strips'!$I$37)*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*('Reel Strips'!$L$28+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$28*('Reel Strips'!$J$28+'Reel Strips'!$J$37)*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*('Reel Strips'!$L$28+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$28*('Reel Strips'!$K$28+'Reel Strips'!$K$37)*('Reel Strips'!$L$28+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$28*('Reel Strips'!$L$28+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$28</f>
         <v/>
       </c>
@@ -6180,12 +6593,12 @@
         <f>Paytable!I8</f>
         <v/>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <f>C16*D16*10</f>
         <v/>
       </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0001544952392578125</v>
+      <c r="F16" s="25" t="n">
+        <v>0.0001158714294433594</v>
       </c>
     </row>
     <row r="17">
@@ -6194,10 +6607,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>'Reel Strips'!$H$29*('Reel Strips'!$I$29+'Reel Strips'!$I$37)*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$29-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$29*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$29-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$29*(1-'Reel Strips'!$K$29-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6205,11 +6618,11 @@
         <f>Paytable!G9</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>C17*D17*10</f>
         <v/>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="25" t="n">
         <v>0.00267791748046875</v>
       </c>
     </row>
@@ -6219,10 +6632,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="23">
         <f>'Reel Strips'!$H$29*('Reel Strips'!$I$29+'Reel Strips'!$I$37)*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$29-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$29*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$29-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$29*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$29-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$29*(1-'Reel Strips'!$L$29-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6230,11 +6643,11 @@
         <f>Paytable!H9</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>C18*D18*10</f>
         <v/>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="25" t="n">
         <v>0.0005214214324951172</v>
       </c>
     </row>
@@ -6244,10 +6657,10 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <f>'Reel Strips'!$H$29*('Reel Strips'!$I$29+'Reel Strips'!$I$37)*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*('Reel Strips'!$L$29+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$29*('Reel Strips'!$J$29+'Reel Strips'!$J$37)*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*('Reel Strips'!$L$29+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$29*('Reel Strips'!$K$29+'Reel Strips'!$K$37)*('Reel Strips'!$L$29+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$29*('Reel Strips'!$L$29+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$29</f>
         <v/>
       </c>
@@ -6255,11 +6668,11 @@
         <f>Paytable!I9</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>C19*D19*10</f>
         <v/>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="25" t="n">
         <v>9.655952453613281e-05</v>
       </c>
     </row>
@@ -6269,10 +6682,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>'Reel Strips'!$H$30*('Reel Strips'!$I$30+'Reel Strips'!$I$37)*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$30-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$30*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$30-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$30*(1-'Reel Strips'!$K$30-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6280,11 +6693,11 @@
         <f>Paytable!G10</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>C20*D20*10</f>
         <v/>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="25" t="n">
         <v>0.001931190490722656</v>
       </c>
     </row>
@@ -6294,10 +6707,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <f>'Reel Strips'!$H$30*('Reel Strips'!$I$30+'Reel Strips'!$I$37)*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$30-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$30*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$30-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$30*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$30-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$30*(1-'Reel Strips'!$L$30-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6305,11 +6718,11 @@
         <f>Paytable!H10</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <f>C21*D21*10</f>
         <v/>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="25" t="n">
         <v>0.000301748514175415</v>
       </c>
     </row>
@@ -6319,10 +6732,10 @@
           <t>Catapult</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>'Reel Strips'!$H$30*('Reel Strips'!$I$30+'Reel Strips'!$I$37)*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*('Reel Strips'!$L$30+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$30*('Reel Strips'!$J$30+'Reel Strips'!$J$37)*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*('Reel Strips'!$L$30+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$30*('Reel Strips'!$K$30+'Reel Strips'!$K$37)*('Reel Strips'!$L$30+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$30*('Reel Strips'!$L$30+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$30</f>
         <v/>
       </c>
@@ -6330,11 +6743,11 @@
         <f>Paytable!I10</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <f>C22*D22*10</f>
         <v/>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="25" t="n">
         <v>5.587935447692871e-05</v>
       </c>
     </row>
@@ -6344,10 +6757,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>'Reel Strips'!$H$31*('Reel Strips'!$I$31+'Reel Strips'!$I$37)*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$31-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$31*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$31-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$31*(1-'Reel Strips'!$K$31-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6355,11 +6768,11 @@
         <f>Paytable!G11</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <f>C23*D23*10</f>
         <v/>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="25" t="n">
         <v>0.001287460327148438</v>
       </c>
     </row>
@@ -6369,10 +6782,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>'Reel Strips'!$H$31*('Reel Strips'!$I$31+'Reel Strips'!$I$37)*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$31-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$31*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$31-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$31*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$31-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$31*(1-'Reel Strips'!$L$31-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6380,11 +6793,11 @@
         <f>Paytable!H11</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <f>C24*D24*10</f>
         <v/>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="25" t="n">
         <v>0.0002086162567138672</v>
       </c>
     </row>
@@ -6394,10 +6807,10 @@
           <t>Landing Net</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>'Reel Strips'!$H$31*('Reel Strips'!$I$31+'Reel Strips'!$I$37)*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*('Reel Strips'!$L$31+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$31*('Reel Strips'!$J$31+'Reel Strips'!$J$37)*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*('Reel Strips'!$L$31+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$31*('Reel Strips'!$K$31+'Reel Strips'!$K$37)*('Reel Strips'!$L$31+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$31*('Reel Strips'!$L$31+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$31</f>
         <v/>
       </c>
@@ -6405,11 +6818,11 @@
         <f>Paytable!I11</f>
         <v/>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <f>C25*D25*10</f>
         <v/>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>2.980232238769531e-05</v>
       </c>
     </row>
@@ -6419,10 +6832,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>'Reel Strips'!$H$32*('Reel Strips'!$I$32+'Reel Strips'!$I$37)*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$32-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$32*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$32-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$32*(1-'Reel Strips'!$K$32-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6430,12 +6843,12 @@
         <f>Paytable!G12</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <f>C26*D26*10</f>
         <v/>
       </c>
-      <c r="F26" s="24" t="n">
-        <v>0.001287460327148438</v>
+      <c r="F26" s="25" t="n">
+        <v>0.0006437301635742188</v>
       </c>
     </row>
     <row r="27">
@@ -6444,10 +6857,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>'Reel Strips'!$H$32*('Reel Strips'!$I$32+'Reel Strips'!$I$37)*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$32-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$32*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$32-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$32*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$32-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$32*(1-'Reel Strips'!$L$32-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6455,12 +6868,12 @@
         <f>Paytable!H12</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>C27*D27*10</f>
         <v/>
       </c>
-      <c r="F27" s="24" t="n">
-        <v>0.0002086162567138672</v>
+      <c r="F27" s="25" t="n">
+        <v>0.0001043081283569336</v>
       </c>
     </row>
     <row r="28">
@@ -6469,10 +6882,10 @@
           <t>Bivvy</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>'Reel Strips'!$H$32*('Reel Strips'!$I$32+'Reel Strips'!$I$37)*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*('Reel Strips'!$L$32+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$32*('Reel Strips'!$J$32+'Reel Strips'!$J$37)*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*('Reel Strips'!$L$32+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$32*('Reel Strips'!$K$32+'Reel Strips'!$K$37)*('Reel Strips'!$L$32+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$32*('Reel Strips'!$L$32+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$32</f>
         <v/>
       </c>
@@ -6480,12 +6893,12 @@
         <f>Paytable!I12</f>
         <v/>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="24">
         <f>C28*D28*10</f>
         <v/>
       </c>
-      <c r="F28" s="24" t="n">
-        <v>2.980232238769531e-05</v>
+      <c r="F28" s="25" t="n">
+        <v>1.490116119384766e-05</v>
       </c>
     </row>
     <row r="29">
@@ -6494,10 +6907,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="23">
         <f>'Reel Strips'!$H$33*('Reel Strips'!$I$33+'Reel Strips'!$I$37)*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$33-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$33*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$33-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$33*(1-'Reel Strips'!$K$33-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6505,11 +6918,11 @@
         <f>Paytable!G13</f>
         <v/>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <f>C29*D29*10</f>
         <v/>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -6519,10 +6932,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="23">
         <f>'Reel Strips'!$H$33*('Reel Strips'!$I$33+'Reel Strips'!$I$37)*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$33-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$33*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$33-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$33*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$33-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$33*(1-'Reel Strips'!$L$33-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6530,11 +6943,11 @@
         <f>Paytable!H13</f>
         <v/>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="24">
         <f>C30*D30*10</f>
         <v/>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -6544,10 +6957,10 @@
           <t>Roach</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>'Reel Strips'!$H$33*('Reel Strips'!$I$33+'Reel Strips'!$I$37)*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*('Reel Strips'!$L$33+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$33*('Reel Strips'!$J$33+'Reel Strips'!$J$37)*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*('Reel Strips'!$L$33+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$33*('Reel Strips'!$K$33+'Reel Strips'!$K$37)*('Reel Strips'!$L$33+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$33*('Reel Strips'!$L$33+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$33</f>
         <v/>
       </c>
@@ -6555,11 +6968,11 @@
         <f>Paytable!I13</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="24">
         <f>C31*D31*10</f>
         <v/>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -6569,10 +6982,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <f>'Reel Strips'!$H$34*('Reel Strips'!$I$34+'Reel Strips'!$I$37)*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$34-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$34*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$34-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$34*(1-'Reel Strips'!$K$34-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6580,11 +6993,11 @@
         <f>Paytable!G14</f>
         <v/>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="24">
         <f>C32*D32*10</f>
         <v/>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -6594,10 +7007,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="23">
         <f>'Reel Strips'!$H$34*('Reel Strips'!$I$34+'Reel Strips'!$I$37)*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$34-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$34*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$34-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$34*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$34-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$34*(1-'Reel Strips'!$L$34-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6605,11 +7018,11 @@
         <f>Paytable!H14</f>
         <v/>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="24">
         <f>C33*D33*10</f>
         <v/>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -6619,10 +7032,10 @@
           <t>Bream</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="23">
         <f>'Reel Strips'!$H$34*('Reel Strips'!$I$34+'Reel Strips'!$I$37)*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*('Reel Strips'!$L$34+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$34*('Reel Strips'!$J$34+'Reel Strips'!$J$37)*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*('Reel Strips'!$L$34+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$34*('Reel Strips'!$K$34+'Reel Strips'!$K$37)*('Reel Strips'!$L$34+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$34*('Reel Strips'!$L$34+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$34</f>
         <v/>
       </c>
@@ -6630,11 +7043,11 @@
         <f>Paytable!I14</f>
         <v/>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="24">
         <f>C34*D34*10</f>
         <v/>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -6644,10 +7057,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <f>'Reel Strips'!$H$35*('Reel Strips'!$I$35+'Reel Strips'!$I$37)*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$35-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$35*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$35-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$35*(1-'Reel Strips'!$K$35-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6655,11 +7068,11 @@
         <f>Paytable!G15</f>
         <v/>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="24">
         <f>C35*D35*10</f>
         <v/>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -6669,10 +7082,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>'Reel Strips'!$H$35*('Reel Strips'!$I$35+'Reel Strips'!$I$37)*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$35-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$35*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$35-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$35*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$35-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$35*(1-'Reel Strips'!$L$35-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6680,11 +7093,11 @@
         <f>Paytable!H15</f>
         <v/>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="24">
         <f>C36*D36*10</f>
         <v/>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -6694,10 +7107,10 @@
           <t>Tench</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="23">
         <f>'Reel Strips'!$H$35*('Reel Strips'!$I$35+'Reel Strips'!$I$37)*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*('Reel Strips'!$L$35+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$35*('Reel Strips'!$J$35+'Reel Strips'!$J$37)*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*('Reel Strips'!$L$35+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$35*('Reel Strips'!$K$35+'Reel Strips'!$K$37)*('Reel Strips'!$L$35+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$35*('Reel Strips'!$L$35+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$35</f>
         <v/>
       </c>
@@ -6705,11 +7118,11 @@
         <f>Paytable!I15</f>
         <v/>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="24">
         <f>C37*D37*10</f>
         <v/>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -6719,10 +7132,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>'Reel Strips'!$H$36*('Reel Strips'!$I$36+'Reel Strips'!$I$37)*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$36-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$36*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*(1-'Reel Strips'!$K$36-'Reel Strips'!$K$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$36*(1-'Reel Strips'!$K$36-'Reel Strips'!$K$37)</f>
         <v/>
       </c>
@@ -6730,11 +7143,11 @@
         <f>Paytable!G16</f>
         <v/>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="24">
         <f>C38*D38*10</f>
         <v/>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="25" t="n">
         <v>0.00042724609375</v>
       </c>
     </row>
@@ -6744,10 +7157,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>'Reel Strips'!$H$36*('Reel Strips'!$I$36+'Reel Strips'!$I$37)*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$36-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$36*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$36-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$36*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*(1-'Reel Strips'!$L$36-'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$36*(1-'Reel Strips'!$L$36-'Reel Strips'!$L$37)</f>
         <v/>
       </c>
@@ -6755,11 +7168,11 @@
         <f>Paytable!H16</f>
         <v/>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="24">
         <f>C39*D39*10</f>
         <v/>
       </c>
-      <c r="F39" s="24" t="n">
+      <c r="F39" s="25" t="n">
         <v>5.53131103515625e-05</v>
       </c>
     </row>
@@ -6769,10 +7182,10 @@
           <t>Mirror Carp</t>
         </is>
       </c>
-      <c r="B40" s="18" t="n">
+      <c r="B40" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>'Reel Strips'!$H$36*('Reel Strips'!$I$36+'Reel Strips'!$I$37)*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*('Reel Strips'!$L$36+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$36*('Reel Strips'!$J$36+'Reel Strips'!$J$37)*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*('Reel Strips'!$L$36+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$36*('Reel Strips'!$K$36+'Reel Strips'!$K$37)*('Reel Strips'!$L$36+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$36*('Reel Strips'!$L$36+'Reel Strips'!$L$37)+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$36+'Reel Strips'!$H$37*'Reel Strips'!$I$37*'Reel Strips'!$J$37*'Reel Strips'!$K$37*'Reel Strips'!$L$37</f>
         <v/>
       </c>
@@ -6780,11 +7193,11 @@
         <f>Paytable!I16</f>
         <v/>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="24">
         <f>C40*D40*10</f>
         <v/>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="25" t="n">
         <v>5.7220458984375e-06</v>
       </c>
     </row>
@@ -6794,7 +7207,7 @@
           <t>Total line RTP</t>
         </is>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="26">
         <f>SUM(E5:E40)</f>
         <v/>
       </c>
@@ -6805,7 +7218,7 @@
           <t>Max difference vs engine exact (should be ~0)</t>
         </is>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <f>SUMPRODUCT(ABS(C5:C40-F5:F40))</f>
         <v/>
       </c>
@@ -6891,21 +7304,21 @@
           <t>2lb 4oz</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="14" t="n">
-        <v>394</v>
-      </c>
-      <c r="D5" s="27">
+      <c r="C5" s="15" t="n">
+        <v>396</v>
+      </c>
+      <c r="D5" s="28">
         <f>C5/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>B5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>1/D5</f>
         <v/>
       </c>
@@ -6916,21 +7329,21 @@
           <t>4lb 0oz</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>C6/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <f>B6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>1/D6</f>
         <v/>
       </c>
@@ -6941,21 +7354,21 @@
           <t>6lb 8oz</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>B7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>1/D7</f>
         <v/>
       </c>
@@ -6966,21 +7379,21 @@
           <t>9lb 12oz</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>110</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>C8/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>B8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>1/D8</f>
         <v/>
       </c>
@@ -6991,21 +7404,21 @@
           <t>14lb 0oz</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>C9/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>B9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>1/D9</f>
         <v/>
       </c>
@@ -7016,21 +7429,21 @@
           <t>19lb 8oz</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>C10/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>B10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>1/D10</f>
         <v/>
       </c>
@@ -7041,21 +7454,21 @@
           <t>26lb 0oz</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>22.5</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f>C11/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>B11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>1/D11</f>
         <v/>
       </c>
@@ -7066,21 +7479,21 @@
           <t>32lb 8oz</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>C12/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>B12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>1/D12</f>
         <v/>
       </c>
@@ -7091,21 +7504,21 @@
           <t>38lb 12oz</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>6.5</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>C13/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>B13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>1/D13</f>
         <v/>
       </c>
@@ -7116,21 +7529,21 @@
           <t>45lb 4oz</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <v>1.75</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>C14/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>B14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>1/D14</f>
         <v/>
       </c>
@@ -7141,21 +7554,21 @@
           <t>52lb 0oz</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>C15/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>B15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>1/D15</f>
         <v/>
       </c>
@@ -7166,21 +7579,21 @@
           <t>64lb 8oz</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>C16/SUM($C$5:$C$16)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>B16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="19">
         <f>1/D16</f>
         <v/>
       </c>
@@ -7191,7 +7604,7 @@
           <t>Mean fish value</t>
         </is>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
@@ -7209,6 +7622,173 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kingfisher (base game random event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>On a base spin the kingfisher may visit: it turns reels 2, 3 and 4 on one random row into Leather Carp wilds, plus any extra spots at random elsewhere on reels 2-5. A spot holding a Bite Alarm keeps the alarm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Chance per base spin</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>0.003333333333333334</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>engine.js KINGFISHER_CHANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Kingfisher: 1 in</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>1/B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Wild spots</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Line win on that spin (x stake)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chance x win</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>7.814400458335875</v>
+      </c>
+      <c r="D8" s="29">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>9.801946942011513</v>
+      </c>
+      <c r="D9" s="29">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>12.39579241474469</v>
+      </c>
+      <c r="D10" s="29">
+        <f>B10*C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Average line win when the kingfisher visits</t>
+        </is>
+      </c>
+      <c r="D11" s="30">
+        <f>SUM(D8:D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Base line RTP without the kingfisher</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>'Line Wins Base'!E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Base game RTP with the kingfisher</t>
+        </is>
+      </c>
+      <c r="B14" s="26">
+        <f>(1-B4)*B13+B4*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Column C is exact: for every row and every set of extra spots, each payline's chance follows from each reel's own symbol chances (a chosen cell is wild, or the reel's alarm), averaged over all of them (math/par_sheet.mjs).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7255,7 +7835,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="32" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7265,7 +7845,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7275,7 +7855,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="32" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7285,7 +7865,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="32" t="n">
         <v>16</v>
       </c>
     </row>
@@ -7295,7 +7875,7 @@
           <t>5 and on</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="32" t="n">
         <v>32</v>
       </c>
     </row>
@@ -7329,304 +7909,304 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="33" t="n">
         <v>0.3637601544156269</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="34">
         <f>B13*C13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="33" t="n">
         <v>0.3844261440607835</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>C13+INDEX($B$5:$B$9,MIN(A14,5))</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="34">
         <f>B14*C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="33" t="n">
         <v>0.1851278757674617</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <f>C14+INDEX($B$5:$B$9,MIN(A15,5))</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="34">
         <f>B15*C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="33" t="n">
         <v>0.05404755225894368</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <f>C15+INDEX($B$5:$B$9,MIN(A16,5))</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="34">
         <f>B16*C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="33" t="n">
         <v>0.01080921979623277</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <f>C16+INDEX($B$5:$B$9,MIN(A17,5))</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="34">
         <f>B17*C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="33" t="n">
         <v>0.001610313370753053</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <f>C17+INDEX($B$5:$B$9,MIN(A18,5))</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="34">
         <f>B18*C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="33" t="n">
         <v>0.0001949131433207399</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <f>C18+INDEX($B$5:$B$9,MIN(A19,5))</f>
         <v/>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="34">
         <f>B19*C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="33" t="n">
         <v>2.125587996630631e-05</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>C19+INDEX($B$5:$B$9,MIN(A20,5))</f>
         <v/>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="34">
         <f>B20*C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="33" t="n">
         <v>2.287645137293226e-06</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>C20+INDEX($B$5:$B$9,MIN(A21,5))</f>
         <v/>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="34">
         <f>B21*C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="33" t="n">
         <v>2.517835619717737e-07</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="19">
         <f>C21+INDEX($B$5:$B$9,MIN(A22,5))</f>
         <v/>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="34">
         <f>B22*C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="33" t="n">
         <v>2.823785851026822e-08</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>C22+INDEX($B$5:$B$9,MIN(A23,5))</f>
         <v/>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="34">
         <f>B23*C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="33" t="n">
         <v>3.217653570359108e-09</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>C23+INDEX($B$5:$B$9,MIN(A24,5))</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <f>B24*C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="33" t="n">
         <v>3.728874515691925e-10</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>C24+INDEX($B$5:$B$9,MIN(A25,5))</f>
         <v/>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="34">
         <f>B25*C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="33" t="n">
         <v>4.386841230578126e-11</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="19">
         <f>C25+INDEX($B$5:$B$9,MIN(A26,5))</f>
         <v/>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="34">
         <f>B26*C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="33" t="n">
         <v>5.226496981111618e-12</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <f>C26+INDEX($B$5:$B$9,MIN(A27,5))</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <f>B27*C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="33" t="n">
         <v>6.296779716656629e-13</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <f>C27+INDEX($B$5:$B$9,MIN(A28,5))</f>
         <v/>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="34">
         <f>B28*C28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="33" t="n">
         <v>7.661575713581199e-14</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="19">
         <f>C28+INDEX($B$5:$B$9,MIN(A29,5))</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="34">
         <f>B29*C29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="33" t="n">
         <v>9.403254323481159e-15</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="19">
         <f>C29+INDEX($B$5:$B$9,MIN(A30,5))</f>
         <v/>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="34">
         <f>B30*C30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="33" t="n">
         <v>1.162968643633572e-15</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <f>C30+INDEX($B$5:$B$9,MIN(A31,5))</f>
         <v/>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="34">
         <f>B31*C31</f>
         <v/>
       </c>
@@ -7637,7 +8217,7 @@
           <t>Total probability (should be 1)</t>
         </is>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="35">
         <f>SUM(B13:B31)</f>
         <v/>
       </c>
@@ -7648,7 +8228,7 @@
           <t>Expected catches per swim</t>
         </is>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="34">
         <f>SUMPRODUCT(A13:A31,B13:B31)</f>
         <v/>
       </c>
@@ -7659,7 +8239,7 @@
           <t>Expected multipliers paid per swim</t>
         </is>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="36">
         <f>SUM(D13:D31)</f>
         <v/>
       </c>
@@ -7676,7 +8256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7727,7 +8307,7 @@
           <t>P(alarm visible) reel 2, base</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7742,7 +8322,7 @@
           <t>P(alarm visible) reel 3, base</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -7753,7 +8333,7 @@
           <t>P(alarm visible) reel 4, base</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -7764,7 +8344,7 @@
           <t>P(trigger) per base spin</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="23">
         <f>B5*B6*B7</f>
         <v/>
       </c>
@@ -7780,7 +8360,7 @@
           <t>Trigger: 1 in</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>1/B8</f>
         <v/>
       </c>
@@ -7792,7 +8372,7 @@
           <t>P(alarm visible) reel 2, free spins</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -7803,7 +8383,7 @@
           <t>P(alarm visible) reel 3, free spins</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -7814,7 +8394,7 @@
           <t>P(alarm visible) reel 4, free spins</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>0.1875</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -7825,7 +8405,7 @@
           <t>P(retrigger) per free spin</t>
         </is>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="23">
         <f>B10*B11*B12</f>
         <v/>
       </c>
@@ -7837,7 +8417,7 @@
           <t>Expected free spins per feature</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="38">
         <f>10/(1-5*B13)</f>
         <v/>
       </c>
@@ -7853,7 +8433,7 @@
           <t>Expected Specimen Fish per free spin</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="22">
         <f>3*SUM('Reel Strips'!H39:L39)</f>
         <v/>
       </c>
@@ -7869,7 +8449,7 @@
           <t>Expected fish in swims per free spin</t>
         </is>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="22">
         <f>3*AVERAGE('Reel Strips'!H39:L39)</f>
         <v/>
       </c>
@@ -7885,7 +8465,7 @@
           <t>Expected fish outside swims per free spin</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <f>B15-B16</f>
         <v/>
       </c>
@@ -7901,7 +8481,7 @@
           <t>Mean fish value</t>
         </is>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="39">
         <f>'Fish Values'!$E$18</f>
         <v/>
       </c>
@@ -7917,7 +8497,7 @@
           <t>Free-spin line RTP per spin</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="39">
         <f>'Line Wins Free Spins'!E41</f>
         <v/>
       </c>
@@ -7933,7 +8513,7 @@
           <t>Expected win per free spin, outside swims</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="29">
         <f>B19+B17*B18</f>
         <v/>
       </c>
@@ -7949,7 +8529,7 @@
           <t>Expected multipliers paid per swim</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="40">
         <f>'Baited Swims'!$B$35</f>
         <v/>
       </c>
@@ -7965,7 +8545,7 @@
           <t>Expected swim win per feature</t>
         </is>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <f>3*B21*B18</f>
         <v/>
       </c>
@@ -7981,7 +8561,7 @@
           <t>Expected feature win (uncapped)</t>
         </is>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="21">
         <f>B14*B20+B22</f>
         <v/>
       </c>
@@ -7997,7 +8577,7 @@
           <t>Feature RTP contribution</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="24">
         <f>B8*B23</f>
         <v/>
       </c>
@@ -8013,384 +8593,13 @@
           <t>Check: catches per swim (spins x chance)</t>
         </is>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>B14*B16/3-'Baited Swims'!$B$34</f>
         <v/>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Should be ~0: links the DP in Baited Swims to the strips</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Win distribution (simulation of the production engine, 50,000,000 rounds, seed 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total win per game round (base spin + any free spins) as a multiple of stake. Rounds counted by math/par_sheet.mjs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Rounds simulated</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="n">
-        <v>50000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Win band</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Rounds</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1 in</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>RTP contribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>No win</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>36948505</v>
-      </c>
-      <c r="C6" s="39">
-        <f>B6/$B$3</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
-        <f>IF(B6=0,"-",$B$3/B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Below stake (0 &lt; x &lt; 1)</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>5573714</v>
-      </c>
-      <c r="C7" s="39">
-        <f>B7/$B$3</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
-        <f>IF(B7=0,"-",$B$3/B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.08542598399929671</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>1x to &lt;2x</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>2743009</v>
-      </c>
-      <c r="C8" s="39">
-        <f>B8/$B$3</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
-        <f>IF(B8=0,"-",$B$3/B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.08095999800032061</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>2x to &lt;5x</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>3496950</v>
-      </c>
-      <c r="C9" s="39">
-        <f>B9/$B$3</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
-        <f>IF(B9=0,"-",$B$3/B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.2193047900032522</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5x to &lt;10x</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n">
-        <v>747100</v>
-      </c>
-      <c r="C10" s="39">
-        <f>B10/$B$3</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>IF(B10=0,"-",$B$3/B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.09974693400006807</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>10x to &lt;20x</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>135842</v>
-      </c>
-      <c r="C11" s="39">
-        <f>B11/$B$3</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
-        <f>IF(B11=0,"-",$B$3/B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.0362322739999931</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>20x to &lt;50x</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>204462</v>
-      </c>
-      <c r="C12" s="39">
-        <f>B12/$B$3</f>
-        <v/>
-      </c>
-      <c r="D12" s="18">
-        <f>IF(B12=0,"-",$B$3/B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.1363402040000143</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>50x to &lt;100x</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>110753</v>
-      </c>
-      <c r="C13" s="39">
-        <f>B13/$B$3</f>
-        <v/>
-      </c>
-      <c r="D13" s="18">
-        <f>IF(B13=0,"-",$B$3/B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.1516287560000053</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>100x to &lt;250x</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>33729</v>
-      </c>
-      <c r="C14" s="39">
-        <f>B14/$B$3</f>
-        <v/>
-      </c>
-      <c r="D14" s="18">
-        <f>IF(B14=0,"-",$B$3/B14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.09439900399999883</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>250x to &lt;500x</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>4578</v>
-      </c>
-      <c r="C15" s="39">
-        <f>B15/$B$3</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>IF(B15=0,"-",$B$3/B15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.02969988400000011</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>500x to &lt;1,000x</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>701</v>
-      </c>
-      <c r="C16" s="39">
-        <f>B16/$B$3</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
-        <f>IF(B16=0,"-",$B$3/B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.009056123999999995</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>1,000x to &lt;5,000x</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>645</v>
-      </c>
-      <c r="C17" s="39">
-        <f>B17/$B$3</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>IF(B17=0,"-",$B$3/B17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.01667745599999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>5,000x (cap)</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C18" s="39">
-        <f>B18/$B$3</f>
-        <v/>
-      </c>
-      <c r="D18" s="18">
-        <f>IF(B18=0,"-",$B$3/B18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.0012</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B19" s="40">
-        <f>SUM(B6:B18)</f>
-        <v/>
-      </c>
-      <c r="C19" s="25">
-        <f>SUM(C6:C18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>SUM(E6:E18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>RTP contribution per band is the simulated sum of wins in that band divided by rounds (input from the simulation).</t>
         </is>
       </c>
     </row>
